--- a/data/Data Kemiskinan.xlsx
+++ b/data/Data Kemiskinan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\jaktimstats-data-main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\jaktimstats_flutter\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6282C14-C80B-4927-99DF-70CBDFC736C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0080E7-9B3C-4403-8322-298953B23869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{541083E4-25B9-4EED-AD62-DC8C7C6B1874}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
   <si>
     <t>DATA STRATEGIS KOTA JAKARTA TIMUR 2010 - 2025</t>
   </si>
@@ -54,10 +54,85 @@
     <t>(000 jiwa)</t>
   </si>
   <si>
+    <t>91.60</t>
+  </si>
+  <si>
+    <t>83.82</t>
+  </si>
+  <si>
+    <t>86.50</t>
+  </si>
+  <si>
+    <t>86.80</t>
+  </si>
+  <si>
+    <t>96.54</t>
+  </si>
+  <si>
+    <t>91.44</t>
+  </si>
+  <si>
+    <t>91.37</t>
+  </si>
+  <si>
+    <t>95.67</t>
+  </si>
+  <si>
+    <t>91.38</t>
+  </si>
+  <si>
+    <t>91.51</t>
+  </si>
+  <si>
+    <t>122.73</t>
+  </si>
+  <si>
+    <t>125.37</t>
+  </si>
+  <si>
+    <t>126.63</t>
+  </si>
+  <si>
+    <t>124.22</t>
+  </si>
+  <si>
+    <t>121.52</t>
+  </si>
+  <si>
+    <t>117.40</t>
+  </si>
+  <si>
     <t>Angka Kemiskinan</t>
   </si>
   <si>
     <t>Persen</t>
+  </si>
+  <si>
+    <t>3.40</t>
+  </si>
+  <si>
+    <t>3.19</t>
+  </si>
+  <si>
+    <t>3.31</t>
+  </si>
+  <si>
+    <t>3.14</t>
+  </si>
+  <si>
+    <t>4.16</t>
+  </si>
+  <si>
+    <t>4.28</t>
+  </si>
+  <si>
+    <t>4.30</t>
+  </si>
+  <si>
+    <t>4.20</t>
+  </si>
+  <si>
+    <t>3.94</t>
   </si>
   <si>
     <t>Kedalaman Kemiskinan (P1)</t>
@@ -66,7 +141,73 @@
     <t>Poin</t>
   </si>
   <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
     <t>Keparahan Kemiskinan (P2)</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>0.20</t>
   </si>
   <si>
     <t>Garis Kemiskinan</t>
@@ -75,17 +216,36 @@
     <t>(Rp/ kapita/ Bulan)</t>
   </si>
   <si>
+    <t>720.813</t>
+  </si>
+  <si>
     <t>Gini Ratio</t>
+  </si>
+  <si>
+    <t>0.399</t>
+  </si>
+  <si>
+    <t>0.376</t>
+  </si>
+  <si>
+    <t>0.363</t>
+  </si>
+  <si>
+    <t>0.374</t>
+  </si>
+  <si>
+    <t>0.420</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\.mm"/>
+    <numFmt numFmtId="165" formatCode="d\.m"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +269,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -137,7 +303,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -154,11 +320,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="mediumDashed">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="mediumDashed">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -194,22 +375,25 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,27 +716,27 @@
     <col min="3" max="3" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -790,327 +974,327 @@
       <c r="C7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="19">
-        <v>91.6</v>
-      </c>
-      <c r="E7" s="19">
-        <v>83.82</v>
-      </c>
-      <c r="F7" s="19">
-        <v>86.5</v>
-      </c>
-      <c r="G7" s="19">
-        <v>86.8</v>
-      </c>
-      <c r="H7" s="19">
-        <v>96.54</v>
-      </c>
-      <c r="I7" s="19">
-        <v>91.44</v>
-      </c>
-      <c r="J7" s="19">
-        <v>91.37</v>
-      </c>
-      <c r="K7" s="19">
-        <v>95.67</v>
-      </c>
-      <c r="L7" s="19">
-        <v>91.38</v>
-      </c>
-      <c r="M7" s="19">
-        <v>91.51</v>
-      </c>
-      <c r="N7" s="19">
-        <v>122.73</v>
-      </c>
-      <c r="O7" s="19">
-        <v>125.37</v>
-      </c>
-      <c r="P7" s="19">
-        <v>126.63</v>
-      </c>
-      <c r="Q7" s="19">
-        <v>124.22</v>
-      </c>
-      <c r="R7" s="19">
-        <v>121.52</v>
-      </c>
-      <c r="S7" s="20">
-        <v>117.4</v>
-      </c>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="15"/>
-      <c r="X7" s="15"/>
-      <c r="Y7" s="15"/>
-      <c r="Z7" s="15"/>
-      <c r="AA7" s="15"/>
+      <c r="D7" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="T7" s="16"/>
+      <c r="U7" s="16"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="16"/>
+      <c r="AA7" s="16"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="12" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="19">
-        <v>3.4</v>
-      </c>
-      <c r="E8" s="19">
-        <v>3.6</v>
-      </c>
-      <c r="F8" s="19">
-        <v>3.12</v>
-      </c>
-      <c r="G8" s="19">
-        <v>3.1</v>
-      </c>
-      <c r="H8" s="19">
-        <v>3.12</v>
-      </c>
-      <c r="I8" s="19">
-        <v>3.1</v>
-      </c>
-      <c r="J8" s="19">
-        <v>3.19</v>
-      </c>
-      <c r="K8" s="19">
-        <v>3.31</v>
-      </c>
-      <c r="L8" s="19">
-        <v>3.14</v>
-      </c>
-      <c r="M8" s="19">
-        <v>3.12</v>
-      </c>
-      <c r="N8" s="19">
-        <v>4.16</v>
-      </c>
-      <c r="O8" s="19">
-        <v>4.28</v>
-      </c>
-      <c r="P8" s="19">
-        <v>4.3</v>
-      </c>
-      <c r="Q8" s="19">
-        <v>4.2</v>
-      </c>
-      <c r="R8" s="19">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="S8" s="20">
-        <v>3.94</v>
-      </c>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="15"/>
-      <c r="Z8" s="15"/>
-      <c r="AA8" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="17">
+        <v>45811</v>
+      </c>
+      <c r="F8" s="18">
+        <v>45994</v>
+      </c>
+      <c r="G8" s="18">
+        <v>45933</v>
+      </c>
+      <c r="H8" s="18">
+        <v>45994</v>
+      </c>
+      <c r="I8" s="18">
+        <v>45933</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="18">
+        <v>45994</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="17">
+        <v>45904</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="12" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="19">
-        <v>0.41</v>
-      </c>
-      <c r="E9" s="19">
-        <v>0.36</v>
-      </c>
-      <c r="F9" s="19">
-        <v>0.36</v>
-      </c>
-      <c r="G9" s="19">
-        <v>0.45</v>
-      </c>
-      <c r="H9" s="19">
-        <v>0.34</v>
-      </c>
-      <c r="I9" s="19">
-        <v>0.5</v>
-      </c>
-      <c r="J9" s="19">
-        <v>0.26</v>
-      </c>
-      <c r="K9" s="19">
-        <v>0.46</v>
-      </c>
-      <c r="L9" s="19">
-        <v>0.36</v>
-      </c>
-      <c r="M9" s="19">
-        <v>0.33</v>
-      </c>
-      <c r="N9" s="19">
-        <v>0.35</v>
-      </c>
-      <c r="O9" s="19">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="P9" s="19">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="Q9" s="19">
-        <v>0.76</v>
-      </c>
-      <c r="R9" s="19">
-        <v>0.33</v>
-      </c>
-      <c r="S9" s="20">
-        <v>0.37</v>
-      </c>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="15"/>
-      <c r="Y9" s="15"/>
-      <c r="Z9" s="15"/>
-      <c r="AA9" s="15"/>
+        <v>34</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="12" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="19">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E10" s="19">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F10" s="19">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G10" s="19">
-        <v>0.11</v>
-      </c>
-      <c r="H10" s="19">
-        <v>0.06</v>
-      </c>
-      <c r="I10" s="19">
-        <v>0.12</v>
-      </c>
-      <c r="J10" s="19">
-        <v>0.04</v>
-      </c>
-      <c r="K10" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="19">
-        <v>0.06</v>
-      </c>
-      <c r="M10" s="19">
-        <v>0.08</v>
-      </c>
-      <c r="N10" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="O10" s="19">
-        <v>0.13</v>
-      </c>
-      <c r="P10" s="19">
-        <v>0.13</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>0.2</v>
-      </c>
-      <c r="R10" s="19">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="S10" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-      <c r="Y10" s="15"/>
-      <c r="Z10" s="15"/>
-      <c r="AA10" s="15"/>
-    </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+    </row>
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="12" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="14">
-        <v>325980</v>
-      </c>
-      <c r="E11" s="14">
-        <v>352614</v>
-      </c>
-      <c r="F11" s="14">
-        <v>366674</v>
-      </c>
-      <c r="G11" s="14">
-        <v>381984</v>
-      </c>
-      <c r="H11" s="14">
-        <v>391205</v>
-      </c>
-      <c r="I11" s="14">
-        <v>412515</v>
-      </c>
-      <c r="J11" s="14">
-        <v>433405</v>
-      </c>
-      <c r="K11" s="14">
-        <v>455584</v>
-      </c>
-      <c r="L11" s="14">
-        <v>502152</v>
-      </c>
-      <c r="M11" s="14">
-        <v>539510</v>
-      </c>
-      <c r="N11" s="14">
-        <v>581954</v>
-      </c>
-      <c r="O11" s="14">
-        <v>594849</v>
-      </c>
-      <c r="P11" s="14">
-        <v>630842</v>
-      </c>
-      <c r="Q11" s="14">
-        <v>669713</v>
-      </c>
-      <c r="R11" s="14">
-        <v>697472</v>
-      </c>
-      <c r="S11" s="21">
-        <v>720813</v>
-      </c>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="15"/>
-      <c r="Y11" s="15"/>
-      <c r="Z11" s="15"/>
-      <c r="AA11" s="15"/>
-    </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="D11" s="13">
+        <v>325.98</v>
+      </c>
+      <c r="E11" s="13">
+        <v>352.61399999999998</v>
+      </c>
+      <c r="F11" s="13">
+        <v>366.67399999999998</v>
+      </c>
+      <c r="G11" s="13">
+        <v>381.98399999999998</v>
+      </c>
+      <c r="H11" s="13">
+        <v>391.20499999999998</v>
+      </c>
+      <c r="I11" s="13">
+        <v>412.51499999999999</v>
+      </c>
+      <c r="J11" s="13">
+        <v>433.40499999999997</v>
+      </c>
+      <c r="K11" s="13">
+        <v>455.584</v>
+      </c>
+      <c r="L11" s="13">
+        <v>502.15199999999999</v>
+      </c>
+      <c r="M11" s="13">
+        <v>539.51</v>
+      </c>
+      <c r="N11" s="13">
+        <v>581.95399999999995</v>
+      </c>
+      <c r="O11" s="13">
+        <v>594.84900000000005</v>
+      </c>
+      <c r="P11" s="13">
+        <v>630.84199999999998</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>669.71299999999997</v>
+      </c>
+      <c r="R11" s="13">
+        <v>697.47199999999998</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+    </row>
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="12" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="13"/>
@@ -1121,34 +1305,34 @@
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
-      <c r="L12" s="19">
-        <v>0.4</v>
-      </c>
-      <c r="M12" s="19">
-        <v>0.38</v>
-      </c>
-      <c r="N12" s="19">
-        <v>0.36</v>
-      </c>
-      <c r="O12" s="19">
-        <v>0.37</v>
-      </c>
-      <c r="P12" s="19">
-        <v>0.37</v>
-      </c>
-      <c r="Q12" s="19">
-        <v>0.42</v>
+      <c r="L12" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="O12" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="P12" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q12" s="22" t="s">
+        <v>66</v>
       </c>
       <c r="R12" s="13"/>
       <c r="S12" s="14"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="15"/>
-      <c r="X12" s="15"/>
-      <c r="Y12" s="15"/>
-      <c r="Z12" s="15"/>
-      <c r="AA12" s="15"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
@@ -1249,7 +1433,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="16"/>
+      <c r="L16" s="19"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -7967,5 +8151,6 @@
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>